--- a/reviews/a-envoyer/otea-filmakers-2026-09-14.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-09-14.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11T06:05:54</t>
+          <t>2026-09-11T09:26:18</t>
         </is>
       </c>
     </row>
